--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:09</t>
+    <t xml:space="preserve">2026-09-09 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:02</t>
+    <t xml:space="preserve">2026-09-17 14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:00</t>
+    <t xml:space="preserve">2026-09-23 12:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:29</t>
+    <t xml:space="preserve">2026-10-02 13:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Chillán Viejo</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:53</t>
+    <t xml:space="preserve">2026-10-04 08:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:50</t>
+    <t xml:space="preserve">2026-10-05 10:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>822040.12</v>
+        <v>822040.13</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>749004.12</v>
+        <v>749004.13</v>
       </c>
     </row>
     <row r="4">
@@ -646,7 +646,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>663989.12</v>
+        <v>663989.13</v>
       </c>
     </row>
     <row r="9">
@@ -765,7 +765,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>623801.62</v>
+        <v>623801.63</v>
       </c>
     </row>
     <row r="16">
@@ -782,7 +782,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>613995.62</v>
+        <v>613995.63</v>
       </c>
     </row>
     <row r="17">
